--- a/output/graficos_dimensiones/comunal_e_supbrut_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_supbrut_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:32</t>
+    <t xml:space="preserve">2026-09-10 00:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_supbrut_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_supbrut_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:39</t>
+    <t xml:space="preserve">2026-09-18 10:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
